--- a/example/Config_link_windows_clean.xlsx
+++ b/example/Config_link_windows_clean.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>error_calib</t>
+          <t>err_rel</t>
         </is>
       </c>
     </row>
@@ -513,20 +513,10 @@
       <c r="G2" t="n">
         <v>250317</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\rnra_gui\src\..\data\temp\250317</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>2.97424389766038</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-17.22668487363041</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.3317077326411412</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,20 +546,10 @@
       <c r="G3" t="n">
         <v>250317</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\rnra_gui\src\..\data\temp\250317</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>2.97424389766038</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-17.22668487363041</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.3317077326411412</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -599,19 +579,181 @@
       <c r="G4" t="n">
         <v>250404</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>C:/Users/forgi/OneDrive - Université de Namur/MASTER 2/Memoire/rnra_gui/tests/test_2\250404</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3.017249565994104</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-19.28458254588099</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.3097481480965906</v>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>251112_1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\data\data\251112\251112\251112</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\251112.xlsx.url</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" t="n">
+        <v>251112</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\rnra_gui\src\..\data\temp\251112</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.378241532812442</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-4.080198973636724</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.9999903071325223</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>251112_2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\data\data\251112\251112\251112</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\251112.xlsx.url</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G6" t="n">
+        <v>251112</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\rnra_gui\src\..\data\temp\251112</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.378241532812442</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-4.080198973636724</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.9999903071325223</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>251112_3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\data\data\251112\251112\251112</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\251112.xlsx.url</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>33</v>
+      </c>
+      <c r="F7" t="n">
+        <v>48</v>
+      </c>
+      <c r="G7" t="n">
+        <v>251112</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\rnra_gui\src\..\data\temp\251112</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.378241532812442</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-4.080198973636724</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.9999903071325223</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>251112_4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\data\data\251112\251112\251112</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\251112.xlsx.url</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>49</v>
+      </c>
+      <c r="F8" t="n">
+        <v>61</v>
+      </c>
+      <c r="G8" t="n">
+        <v>251112</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\rnra_gui\src\..\data\temp\251112</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.378241532812442</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-4.080198973636724</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.9999903071325223</v>
       </c>
     </row>
   </sheetData>

--- a/example/Config_link_windows_clean.xlsx
+++ b/example/Config_link_windows_clean.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>err_rel</t>
+          <t>error_calib</t>
         </is>
       </c>
     </row>
@@ -513,10 +513,20 @@
       <c r="G2" t="n">
         <v>250317</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>C:/Users/forgi/OneDrive - Université de Namur/MASTER 2/Memoire/rnra_gui/example/20260430\250317</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>2.948312783327458</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-8.088918884032058</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.328839764380488</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -546,10 +556,20 @@
       <c r="G3" t="n">
         <v>250317</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>C:/Users/forgi/OneDrive - Université de Namur/MASTER 2/Memoire/rnra_gui/example/20260430\250317</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2.948312783327458</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-8.088918884032058</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.328839764380488</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -614,17 +634,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\rnra_gui\src\..\data\temp\251112</t>
+          <t>C:/Users/forgi/OneDrive - Université de Namur/MASTER 2/Memoire/rnra_gui/example/20260430\251112</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.378241532812442</v>
+        <v>3.400911007294158</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.080198973636724</v>
+        <v>-11.72391201414656</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9999903071325223</v>
+        <v>0.382757438308858</v>
       </c>
     </row>
     <row r="6">
@@ -657,17 +677,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\rnra_gui\src\..\data\temp\251112</t>
+          <t>C:/Users/forgi/OneDrive - Université de Namur/MASTER 2/Memoire/rnra_gui/example/20260430\251112</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.378241532812442</v>
+        <v>3.400911007294158</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.080198973636724</v>
+        <v>-11.72391201414656</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9999903071325223</v>
+        <v>0.382757438308858</v>
       </c>
     </row>
     <row r="7">
@@ -700,17 +720,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\rnra_gui\src\..\data\temp\251112</t>
+          <t>C:/Users/forgi/OneDrive - Université de Namur/MASTER 2/Memoire/rnra_gui/example/20260430\251112</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.378241532812442</v>
+        <v>3.400911007294158</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.080198973636724</v>
+        <v>-11.72391201414656</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9999903071325223</v>
+        <v>0.382757438308858</v>
       </c>
     </row>
     <row r="8">
@@ -743,17 +763,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\rnra_gui\src\..\data\temp\251112</t>
+          <t>C:/Users/forgi/OneDrive - Université de Namur/MASTER 2/Memoire/rnra_gui/example/20260430\251112</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.378241532812442</v>
+        <v>3.400911007294158</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.080198973636724</v>
+        <v>-11.72391201414656</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9999903071325223</v>
+        <v>0.382757438308858</v>
       </c>
     </row>
   </sheetData>

--- a/example/Config_link_windows_clean.xlsx
+++ b/example/Config_link_windows_clean.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,17 +515,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>C:/Users/forgi/OneDrive - Université de Namur/MASTER 2/Memoire/rnra_gui/example/20260430\250317</t>
+          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\rnra_gui\src\..\data\temp\250317</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.948312783327458</v>
+        <v>2.949101315820768</v>
       </c>
       <c r="J2" t="n">
-        <v>-8.088918884032058</v>
+        <v>-8.517423412978149</v>
       </c>
       <c r="K2" t="n">
-        <v>0.328839764380488</v>
+        <v>0.3267565101565981</v>
       </c>
     </row>
     <row r="3">
@@ -558,17 +558,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C:/Users/forgi/OneDrive - Université de Namur/MASTER 2/Memoire/rnra_gui/example/20260430\250317</t>
+          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\rnra_gui\src\..\data\temp\250317</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.948312783327458</v>
+        <v>2.949101315820768</v>
       </c>
       <c r="J3" t="n">
-        <v>-8.088918884032058</v>
+        <v>-8.517423412978149</v>
       </c>
       <c r="K3" t="n">
-        <v>0.328839764380488</v>
+        <v>0.3267565101565981</v>
       </c>
     </row>
     <row r="4">
@@ -604,178 +604,6 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>251112_1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\data\data\251112\251112\251112</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\251112.xlsx.url</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G5" t="n">
-        <v>251112</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>C:/Users/forgi/OneDrive - Université de Namur/MASTER 2/Memoire/rnra_gui/example/20260430\251112</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.400911007294158</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-11.72391201414656</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.382757438308858</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>251112_2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\data\data\251112\251112\251112</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\251112.xlsx.url</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>21</v>
-      </c>
-      <c r="F6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G6" t="n">
-        <v>251112</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>C:/Users/forgi/OneDrive - Université de Namur/MASTER 2/Memoire/rnra_gui/example/20260430\251112</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3.400911007294158</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-11.72391201414656</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.382757438308858</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>251112_3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\data\data\251112\251112\251112</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\251112.xlsx.url</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>33</v>
-      </c>
-      <c r="F7" t="n">
-        <v>48</v>
-      </c>
-      <c r="G7" t="n">
-        <v>251112</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>C:/Users/forgi/OneDrive - Université de Namur/MASTER 2/Memoire/rnra_gui/example/20260430\251112</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.400911007294158</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-11.72391201414656</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.382757438308858</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>251112_4</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\data\data\251112\251112\251112</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>C:\Users\forgi\OneDrive - Université de Namur\MASTER 2\Memoire\251112.xlsx.url</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>49</v>
-      </c>
-      <c r="F8" t="n">
-        <v>61</v>
-      </c>
-      <c r="G8" t="n">
-        <v>251112</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>C:/Users/forgi/OneDrive - Université de Namur/MASTER 2/Memoire/rnra_gui/example/20260430\251112</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.400911007294158</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-11.72391201414656</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.382757438308858</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
